--- a/docs/Työajan seuranta.xlsx
+++ b/docs/Työajan seuranta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kimi\Downloads\j\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Panu\Desktop\webprojekti\web-sovellusprojekti-ryhma3\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2E6C0D-5D07-4E8D-8C28-4BB29619FE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3C3D79-6FE3-4708-A26F-5880A1BBDD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3810" yWindow="3810" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
+    <workbookView xWindow="3960" yWindow="2490" windowWidth="21600" windowHeight="11385" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Panu" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="34">
   <si>
     <t>Pvm</t>
   </si>
@@ -118,6 +118,30 @@
   </si>
   <si>
     <t>Dokumentointi</t>
+  </si>
+  <si>
+    <t>UI suunnittelu</t>
+  </si>
+  <si>
+    <t>UI Wireframe luonti</t>
+  </si>
+  <si>
+    <t>Tällä hetkellä pyörivien elokuvien lista sivun luonti</t>
+  </si>
+  <si>
+    <t>Pyörivien elokuvien listan .css päivitys</t>
+  </si>
+  <si>
+    <t>Lisättiin sisäänkirjautumis vaatimus joillekkin sivuille</t>
+  </si>
+  <si>
+    <t>Yksittäinen sivu kaikille elokuville</t>
+  </si>
+  <si>
+    <t>Localstorage versio elokuvien arvosteluista</t>
+  </si>
+  <si>
+    <t>Elokuvien arvostelu sivun uudelleen tekeminen backend yhteydellä</t>
   </si>
 </sst>
 </file>
@@ -159,7 +183,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -476,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCCA3CA-2A17-42EC-86E5-CF5FE2A8D439}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -504,13 +530,103 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+      <c r="A3" s="3">
+        <v>45967</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
+      <c r="A4" s="3">
+        <v>45968</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
+      <c r="A5" s="3">
+        <v>45974</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>45976</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>45979</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>45981</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>45982</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>45985</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>46008</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/Työajan seuranta.xlsx
+++ b/docs/Työajan seuranta.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Panu\Desktop\webprojekti\web-sovellusprojekti-ryhma3\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\web-sovellusprojekti-ryhma3\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3C3D79-6FE3-4708-A26F-5880A1BBDD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3F9F18-E70B-4C26-9E99-17B84E34B5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="2490" windowWidth="21600" windowHeight="11385" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="4" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Panu" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="43">
   <si>
     <t>Pvm</t>
   </si>
@@ -142,6 +142,33 @@
   </si>
   <si>
     <t>Elokuvien arvostelu sivun uudelleen tekeminen backend yhteydellä</t>
+  </si>
+  <si>
+    <t>Ryhmien perusteet</t>
+  </si>
+  <si>
+    <t>Ryhmien liittymispyynnöt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryhmän jäsenten poisto </t>
+  </si>
+  <si>
+    <t>Viimeistely</t>
+  </si>
+  <si>
+    <t>Kirjautumissivujen .css</t>
+  </si>
+  <si>
+    <t>Yleinen .css</t>
+  </si>
+  <si>
+    <t>2h</t>
+  </si>
+  <si>
+    <t>3h</t>
+  </si>
+  <si>
+    <t>1h</t>
   </si>
 </sst>
 </file>
@@ -183,14 +210,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normaali" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -206,7 +231,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 -teema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -530,101 +555,101 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>45967</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>45968</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>45974</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>45976</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+      <c r="A7" s="1">
         <v>45979</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>45981</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="A9" s="1">
         <v>45982</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+      <c r="A10" s="1">
         <v>45985</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+      <c r="A11" s="1">
         <v>46008</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11">
         <v>1</v>
       </c>
     </row>
@@ -951,7 +976,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B26443-D637-4066-AFDB-D04119BEB5CE}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -979,10 +1004,114 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>45988</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>45995</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>45999</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46006</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46009</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/Työajan seuranta.xlsx
+++ b/docs/Työajan seuranta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\web-sovellusprojekti-ryhma3\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joelr\Downloads\web-sovellusprojekti-ryhma3-main newest\web-sovellusprojekti-ryhma3-main\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3F9F18-E70B-4C26-9E99-17B84E34B5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCCB5778-2DD7-4B17-8FC1-F427CC011955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="4" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Panu" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="50">
   <si>
     <t>Pvm</t>
   </si>
@@ -169,6 +169,27 @@
   </si>
   <si>
     <t>1h</t>
+  </si>
+  <si>
+    <t>Projektin suunnittelua, työjako, yms.</t>
+  </si>
+  <si>
+    <t>Tutustumista movie API rajapintaan</t>
+  </si>
+  <si>
+    <t>Haku ominaisuuden aloitus</t>
+  </si>
+  <si>
+    <t>Haku ominaisuuden jatkaminen (UI)</t>
+  </si>
+  <si>
+    <t>Lisää css säätöä haku palkissa</t>
+  </si>
+  <si>
+    <t>Backend funktiot haulle</t>
+  </si>
+  <si>
+    <t>Filtterien teko ja viimeistely</t>
   </si>
 </sst>
 </file>
@@ -893,7 +914,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1EECD9-4AD3-41AF-8923-B28678799497}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
@@ -921,13 +942,81 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1">
+        <v>45967</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1">
+        <v>45968</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>45985</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
